--- a/BVSimulationFiles/89.xlsx
+++ b/BVSimulationFiles/89.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0001457627118644068</v>
+        <v>0.0002915254237288136</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001693131132917038</v>
+        <v>0.0003386262265834076</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001928635147190009</v>
+        <v>0.0003857270294380018</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002164139161462979</v>
+        <v>0.0004328278322925958</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000239964317573595</v>
+        <v>0.00047992863514719</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000263514719000892</v>
+        <v>0.000527029438001784</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000287065120428189</v>
+        <v>0.000574130240856378</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003106155218554861</v>
+        <v>0.0006212310437109722</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003341659232827832</v>
+        <v>0.0006683318465655664</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0003577163247100803</v>
+        <v>0.0007154326494201606</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003812667261373773</v>
+        <v>0.0007625334522747546</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0004048171275646743</v>
+        <v>0.0008096342551293486</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0004283675289919714</v>
+        <v>0.0008567350579839428</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0004519179304192685</v>
+        <v>0.000903835860838537</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0004754683318465655</v>
+        <v>0.000950936663693131</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0004990187332738625</v>
+        <v>0.0009980374665477249</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0005225691347011596</v>
+        <v>0.001045138269402319</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0005461195361284567</v>
+        <v>0.001092239072256913</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0005696699375557537</v>
+        <v>0.001139339875111507</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0005932203389830508</v>
+        <v>0.001186440677966102</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0001457627118644068</v>
+        <v>0.0002915254237288136</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0001693131132917038</v>
+        <v>0.0003386262265834076</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0001928635147190009</v>
+        <v>0.0003857270294380018</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002164139161462979</v>
+        <v>0.0004328278322925958</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000239964317573595</v>
+        <v>0.00047992863514719</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000263514719000892</v>
+        <v>0.000527029438001784</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000287065120428189</v>
+        <v>0.000574130240856378</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003106155218554861</v>
+        <v>0.0006212310437109722</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003341659232827832</v>
+        <v>0.0006683318465655664</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0003577163247100803</v>
+        <v>0.0007154326494201606</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003812667261373773</v>
+        <v>0.0007625334522747546</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004048171275646743</v>
+        <v>0.0008096342551293486</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0004283675289919714</v>
+        <v>0.0008567350579839428</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0004519179304192685</v>
+        <v>0.000903835860838537</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0004754683318465655</v>
+        <v>0.000950936663693131</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0004990187332738625</v>
+        <v>0.0009980374665477249</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0005225691347011596</v>
+        <v>0.001045138269402319</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0005461195361284567</v>
+        <v>0.001092239072256913</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0005696699375557537</v>
+        <v>0.001139339875111507</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0005932203389830508</v>
+        <v>0.001186440677966102</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/89.xlsx
+++ b/BVSimulationFiles/89.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0002915254237288136</v>
+        <v>0.002915254237288136</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003386262265834076</v>
+        <v>0.003386262265834076</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0003857270294380018</v>
+        <v>0.003857270294380018</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004328278322925958</v>
+        <v>0.004328278322925958</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00047992863514719</v>
+        <v>0.0047992863514719</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000527029438001784</v>
+        <v>0.00527029438001784</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000574130240856378</v>
+        <v>0.00574130240856378</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0006212310437109722</v>
+        <v>0.006212310437109722</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0006683318465655664</v>
+        <v>0.006683318465655664</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007154326494201606</v>
+        <v>0.007154326494201606</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007625334522747546</v>
+        <v>0.007625334522747546</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008096342551293486</v>
+        <v>0.008096342551293486</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008567350579839428</v>
+        <v>0.008567350579839428</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000903835860838537</v>
+        <v>0.00903835860838537</v>
       </c>
       <c r="P2" t="n">
-        <v>0.000950936663693131</v>
+        <v>0.00950936663693131</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0009980374665477249</v>
+        <v>0.00998037466547725</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001045138269402319</v>
+        <v>0.01045138269402319</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001092239072256913</v>
+        <v>0.01092239072256913</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001139339875111507</v>
+        <v>0.01139339875111507</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001186440677966102</v>
+        <v>0.01186440677966102</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0002915254237288136</v>
+        <v>0.002915254237288136</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0003386262265834076</v>
+        <v>0.003386262265834076</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0003857270294380018</v>
+        <v>0.003857270294380018</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004328278322925958</v>
+        <v>0.004328278322925958</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00047992863514719</v>
+        <v>0.0047992863514719</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000527029438001784</v>
+        <v>0.00527029438001784</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000574130240856378</v>
+        <v>0.00574130240856378</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006212310437109722</v>
+        <v>0.006212310437109722</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006683318465655664</v>
+        <v>0.006683318465655664</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007154326494201606</v>
+        <v>0.007154326494201606</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007625334522747546</v>
+        <v>0.007625334522747546</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0008096342551293486</v>
+        <v>0.008096342551293486</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008567350579839428</v>
+        <v>0.008567350579839428</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000903835860838537</v>
+        <v>0.00903835860838537</v>
       </c>
       <c r="P3" t="n">
-        <v>0.000950936663693131</v>
+        <v>0.00950936663693131</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0009980374665477249</v>
+        <v>0.00998037466547725</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001045138269402319</v>
+        <v>0.01045138269402319</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001092239072256913</v>
+        <v>0.01092239072256913</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001139339875111507</v>
+        <v>0.01139339875111507</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001186440677966102</v>
+        <v>0.01186440677966102</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/89.xlsx
+++ b/BVSimulationFiles/89.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,60 +421,90 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.002356842105263158</v>
+        <v>0.001544137931034483</v>
       </c>
       <c r="D1" t="n">
-        <v>0.004713684210526315</v>
+        <v>0.003088275862068965</v>
       </c>
       <c r="E1" t="n">
-        <v>0.007070526315789474</v>
+        <v>0.004632413793103449</v>
       </c>
       <c r="F1" t="n">
-        <v>0.00942736842105263</v>
+        <v>0.006176551724137931</v>
       </c>
       <c r="G1" t="n">
-        <v>0.01178421052631579</v>
+        <v>0.007720689655172414</v>
       </c>
       <c r="H1" t="n">
-        <v>0.01414105263157895</v>
+        <v>0.009264827586206897</v>
       </c>
       <c r="I1" t="n">
-        <v>0.0164978947368421</v>
+        <v>0.01080896551724138</v>
       </c>
       <c r="J1" t="n">
-        <v>0.01885473684210526</v>
+        <v>0.01235310344827586</v>
       </c>
       <c r="K1" t="n">
-        <v>0.02121157894736842</v>
+        <v>0.01389724137931034</v>
       </c>
       <c r="L1" t="n">
-        <v>0.02356842105263158</v>
+        <v>0.01544137931034483</v>
       </c>
       <c r="M1" t="n">
-        <v>0.02592526315789474</v>
+        <v>0.01698551724137931</v>
       </c>
       <c r="N1" t="n">
-        <v>0.0282821052631579</v>
+        <v>0.01852965517241379</v>
       </c>
       <c r="O1" t="n">
-        <v>0.03063894736842105</v>
+        <v>0.02007379310344827</v>
       </c>
       <c r="P1" t="n">
-        <v>0.03299578947368421</v>
+        <v>0.02161793103448276</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.03535263157894736</v>
+        <v>0.02316206896551724</v>
       </c>
       <c r="R1" t="n">
-        <v>0.03770947368421052</v>
+        <v>0.02470620689655172</v>
       </c>
       <c r="S1" t="n">
-        <v>0.04006631578947368</v>
+        <v>0.02625034482758621</v>
       </c>
       <c r="T1" t="n">
-        <v>0.04242315789473684</v>
+        <v>0.02779448275862069</v>
       </c>
       <c r="U1" t="n">
+        <v>0.02933862068965517</v>
+      </c>
+      <c r="V1" t="n">
+        <v>0.03088275862068966</v>
+      </c>
+      <c r="W1" t="n">
+        <v>0.03242689655172414</v>
+      </c>
+      <c r="X1" t="n">
+        <v>0.03397103448275862</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>0.0355151724137931</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>0.03705931034482759</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>0.03860344827586207</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>0.04014758620689655</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>0.04169172413793103</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>0.04323586206896552</v>
+      </c>
+      <c r="AE1" t="n">
         <v>0.04478</v>
       </c>
     </row>
@@ -483,64 +513,94 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.002915254237288136</v>
+        <v>0.0157280380418305</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003386262265834076</v>
+        <v>0.01739291456269789</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003857270294380018</v>
+        <v>0.01905779108356527</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004328278322925958</v>
+        <v>0.02072266760443265</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0047992863514719</v>
+        <v>0.02238754412530004</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00527029438001784</v>
+        <v>0.02405242064616742</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00574130240856378</v>
+        <v>0.0257172971670348</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006212310437109722</v>
+        <v>0.02738217368790219</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006683318465655664</v>
+        <v>0.02904705020876957</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007154326494201606</v>
+        <v>0.03071192672963695</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007625334522747546</v>
+        <v>0.03237680325050434</v>
       </c>
       <c r="M2" t="n">
-        <v>0.008096342551293486</v>
+        <v>0.03404167977137171</v>
       </c>
       <c r="N2" t="n">
-        <v>0.008567350579839428</v>
+        <v>0.03570655629223909</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00903835860838537</v>
+        <v>0.03737143281310648</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00950936663693131</v>
+        <v>0.03903630933397387</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00998037466547725</v>
+        <v>0.04070118585484125</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01045138269402319</v>
+        <v>0.04236606237570863</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01092239072256913</v>
+        <v>0.04403093889657601</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01139339875111507</v>
+        <v>0.04569581541744339</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01186440677966102</v>
+        <v>0.04736069193831078</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.04902556845917817</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.05069044498004555</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.05235532150091293</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.05402019802178032</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.05568507454264769</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.05734995106351508</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.05901482758438246</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.06067970410524984</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.06234458062611723</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.06400945714698461</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +608,94 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002915254237288136</v>
+        <v>0.0157280380418305</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003386262265834076</v>
+        <v>0.01739291456269789</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003857270294380018</v>
+        <v>0.01905779108356527</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004328278322925958</v>
+        <v>0.02072266760443265</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0047992863514719</v>
+        <v>0.02238754412530004</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00527029438001784</v>
+        <v>0.02405242064616742</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00574130240856378</v>
+        <v>0.0257172971670348</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006212310437109722</v>
+        <v>0.02738217368790219</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006683318465655664</v>
+        <v>0.02904705020876957</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007154326494201606</v>
+        <v>0.03071192672963695</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007625334522747546</v>
+        <v>0.03237680325050434</v>
       </c>
       <c r="M3" t="n">
-        <v>0.008096342551293486</v>
+        <v>0.03404167977137171</v>
       </c>
       <c r="N3" t="n">
-        <v>0.008567350579839428</v>
+        <v>0.03570655629223909</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00903835860838537</v>
+        <v>0.03737143281310648</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00950936663693131</v>
+        <v>0.03903630933397387</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00998037466547725</v>
+        <v>0.04070118585484125</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01045138269402319</v>
+        <v>0.04236606237570863</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01092239072256913</v>
+        <v>0.04403093889657601</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01139339875111507</v>
+        <v>0.04569581541744339</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01186440677966102</v>
+        <v>0.04736069193831078</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.04902556845917817</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.05069044498004555</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.05235532150091293</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.05402019802178032</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.05568507454264769</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.05734995106351508</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.05901482758438246</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.06067970410524984</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.06234458062611723</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.06400945714698461</v>
       </c>
     </row>
   </sheetData>
